--- a/artfynd/A 10058-2026 artfynd.xlsx
+++ b/artfynd/A 10058-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132050849</v>
       </c>
       <c r="B2" t="n">
-        <v>83248</v>
+        <v>83249</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132050871</v>
       </c>
       <c r="B3" t="n">
-        <v>99046</v>
+        <v>99047</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>132050879</v>
       </c>
       <c r="B4" t="n">
-        <v>99046</v>
+        <v>99047</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132050881</v>
+        <v>132050856</v>
       </c>
       <c r="B5" t="n">
-        <v>91836</v>
+        <v>91841</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478332</v>
+        <v>478378</v>
       </c>
       <c r="R5" t="n">
-        <v>6991429</v>
+        <v>6991412</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132050856</v>
+        <v>132050881</v>
       </c>
       <c r="B6" t="n">
-        <v>91840</v>
+        <v>91837</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478378</v>
+        <v>478332</v>
       </c>
       <c r="R6" t="n">
-        <v>6991412</v>
+        <v>6991429</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
         <v>132050863</v>
       </c>
       <c r="B7" t="n">
-        <v>78280</v>
+        <v>78281</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>132050855</v>
       </c>
       <c r="B8" t="n">
-        <v>91840</v>
+        <v>91841</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>132050858</v>
       </c>
       <c r="B9" t="n">
-        <v>57906</v>
+        <v>57907</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>132050860</v>
       </c>
       <c r="B10" t="n">
-        <v>57906</v>
+        <v>57907</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>132050878</v>
       </c>
       <c r="B11" t="n">
-        <v>99046</v>
+        <v>99047</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>132050872</v>
       </c>
       <c r="B12" t="n">
-        <v>99046</v>
+        <v>99047</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1772,10 +1772,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132050851</v>
+        <v>132050854</v>
       </c>
       <c r="B13" t="n">
-        <v>83248</v>
+        <v>91841</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1783,21 +1783,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1807,10 +1807,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478417</v>
+        <v>478328</v>
       </c>
       <c r="R13" t="n">
-        <v>6991565</v>
+        <v>6991491</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1869,10 +1869,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132050854</v>
+        <v>132050851</v>
       </c>
       <c r="B14" t="n">
-        <v>91840</v>
+        <v>83249</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1880,21 +1880,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478328</v>
+        <v>478417</v>
       </c>
       <c r="R14" t="n">
-        <v>6991491</v>
+        <v>6991565</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1969,7 +1969,7 @@
         <v>132050865</v>
       </c>
       <c r="B15" t="n">
-        <v>78280</v>
+        <v>78281</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>132050870</v>
       </c>
       <c r="B16" t="n">
-        <v>99046</v>
+        <v>99047</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>132050873</v>
       </c>
       <c r="B17" t="n">
-        <v>99046</v>
+        <v>99047</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>132050861</v>
       </c>
       <c r="B18" t="n">
-        <v>57906</v>
+        <v>57907</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 10058-2026 artfynd.xlsx
+++ b/artfynd/A 10058-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132050849</v>
       </c>
       <c r="B2" t="n">
-        <v>83249</v>
+        <v>83254</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132050871</v>
       </c>
       <c r="B3" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>132050879</v>
       </c>
       <c r="B4" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>132050856</v>
       </c>
       <c r="B5" t="n">
-        <v>91841</v>
+        <v>91846</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>132050881</v>
       </c>
       <c r="B6" t="n">
-        <v>91837</v>
+        <v>91842</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>132050863</v>
       </c>
       <c r="B7" t="n">
-        <v>78281</v>
+        <v>78286</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>132050855</v>
       </c>
       <c r="B8" t="n">
-        <v>91841</v>
+        <v>91846</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>132050858</v>
       </c>
       <c r="B9" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>132050860</v>
       </c>
       <c r="B10" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>132050878</v>
       </c>
       <c r="B11" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>132050872</v>
       </c>
       <c r="B12" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1772,10 +1772,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132050854</v>
+        <v>132050851</v>
       </c>
       <c r="B13" t="n">
-        <v>91841</v>
+        <v>83254</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1783,21 +1783,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1807,10 +1807,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478328</v>
+        <v>478417</v>
       </c>
       <c r="R13" t="n">
-        <v>6991491</v>
+        <v>6991565</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1869,10 +1869,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132050851</v>
+        <v>132050854</v>
       </c>
       <c r="B14" t="n">
-        <v>83249</v>
+        <v>91846</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1880,21 +1880,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478417</v>
+        <v>478328</v>
       </c>
       <c r="R14" t="n">
-        <v>6991565</v>
+        <v>6991491</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1969,7 +1969,7 @@
         <v>132050865</v>
       </c>
       <c r="B15" t="n">
-        <v>78281</v>
+        <v>78286</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>132050870</v>
       </c>
       <c r="B16" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>132050873</v>
       </c>
       <c r="B17" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>132050861</v>
       </c>
       <c r="B18" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 10058-2026 artfynd.xlsx
+++ b/artfynd/A 10058-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132050849</v>
       </c>
       <c r="B2" t="n">
-        <v>83254</v>
+        <v>83256</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132050871</v>
       </c>
       <c r="B3" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>132050879</v>
       </c>
       <c r="B4" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>132050856</v>
       </c>
       <c r="B5" t="n">
-        <v>91846</v>
+        <v>91848</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>132050881</v>
       </c>
       <c r="B6" t="n">
-        <v>91842</v>
+        <v>91844</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>132050863</v>
       </c>
       <c r="B7" t="n">
-        <v>78286</v>
+        <v>78288</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>132050855</v>
       </c>
       <c r="B8" t="n">
-        <v>91846</v>
+        <v>91848</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>132050858</v>
       </c>
       <c r="B9" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>132050860</v>
       </c>
       <c r="B10" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>132050878</v>
       </c>
       <c r="B11" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>132050872</v>
       </c>
       <c r="B12" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>132050851</v>
       </c>
       <c r="B13" t="n">
-        <v>83254</v>
+        <v>83256</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>132050854</v>
       </c>
       <c r="B14" t="n">
-        <v>91846</v>
+        <v>91848</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>132050865</v>
       </c>
       <c r="B15" t="n">
-        <v>78286</v>
+        <v>78288</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>132050870</v>
       </c>
       <c r="B16" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>132050873</v>
       </c>
       <c r="B17" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>132050861</v>
       </c>
       <c r="B18" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 10058-2026 artfynd.xlsx
+++ b/artfynd/A 10058-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132050849</v>
+        <v>132616026</v>
       </c>
       <c r="B2" t="n">
-        <v>83307</v>
+        <v>89354</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Svartsjöarna, Jmt</t>
+          <t>Måläng, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478360</v>
+        <v>478401</v>
       </c>
       <c r="R2" t="n">
-        <v>6991519</v>
+        <v>6991457</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132050871</v>
+        <v>132050881</v>
       </c>
       <c r="B3" t="n">
-        <v>99118</v>
+        <v>91970</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478389</v>
+        <v>478332</v>
       </c>
       <c r="R3" t="n">
-        <v>6991445</v>
+        <v>6991429</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Åtminstone 10 plantor</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132050879</v>
+        <v>132050854</v>
       </c>
       <c r="B4" t="n">
-        <v>99118</v>
+        <v>91974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478374</v>
+        <v>478328</v>
       </c>
       <c r="R4" t="n">
-        <v>6991445</v>
+        <v>6991491</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Utspritt 30 + plantor</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132050856</v>
+        <v>132050855</v>
       </c>
       <c r="B5" t="n">
-        <v>91909</v>
+        <v>91974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478378</v>
+        <v>478386</v>
       </c>
       <c r="R5" t="n">
-        <v>6991412</v>
+        <v>6991440</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132050881</v>
+        <v>132050856</v>
       </c>
       <c r="B6" t="n">
-        <v>91905</v>
+        <v>91974</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478332</v>
+        <v>478378</v>
       </c>
       <c r="R6" t="n">
-        <v>6991429</v>
+        <v>6991412</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132050863</v>
+        <v>132050849</v>
       </c>
       <c r="B7" t="n">
-        <v>78339</v>
+        <v>83358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478349</v>
+        <v>478360</v>
       </c>
       <c r="R7" t="n">
-        <v>6991499</v>
+        <v>6991519</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1267,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132050855</v>
+        <v>132050851</v>
       </c>
       <c r="B8" t="n">
-        <v>91909</v>
+        <v>83358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478386</v>
+        <v>478417</v>
       </c>
       <c r="R8" t="n">
-        <v>6991440</v>
+        <v>6991565</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1367,7 +1357,7 @@
         <v>132050858</v>
       </c>
       <c r="B9" t="n">
-        <v>57953</v>
+        <v>57975</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1466,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132050878</v>
+        <v>132050860</v>
       </c>
       <c r="B10" t="n">
-        <v>99118</v>
+        <v>57975</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1501,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478412</v>
+        <v>478440</v>
       </c>
       <c r="R10" t="n">
-        <v>6991427</v>
+        <v>6991467</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1541,7 +1531,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Mer än 25 st plantor</t>
+          <t>Ringhack, äldre, på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1568,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132050860</v>
+        <v>132050861</v>
       </c>
       <c r="B11" t="n">
-        <v>57953</v>
+        <v>57975</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1603,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478440</v>
+        <v>478453</v>
       </c>
       <c r="R11" t="n">
-        <v>6991467</v>
+        <v>6991448</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1643,7 +1633,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran</t>
+          <t>Ringhack, färska, på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1670,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132050872</v>
+        <v>132050870</v>
       </c>
       <c r="B12" t="n">
-        <v>99118</v>
+        <v>99195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1705,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478304</v>
+        <v>478419</v>
       </c>
       <c r="R12" t="n">
-        <v>6991437</v>
+        <v>6991510</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1741,11 +1731,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Mer än 20 plantor</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1772,32 +1757,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132050854</v>
+        <v>132050871</v>
       </c>
       <c r="B13" t="n">
-        <v>91909</v>
+        <v>99195</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1807,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478328</v>
+        <v>478389</v>
       </c>
       <c r="R13" t="n">
-        <v>6991491</v>
+        <v>6991445</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1843,6 +1828,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Åtminstone 10 plantor</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1869,32 +1859,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132050851</v>
+        <v>132050872</v>
       </c>
       <c r="B14" t="n">
-        <v>83307</v>
+        <v>99195</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1904,10 +1894,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478417</v>
+        <v>478304</v>
       </c>
       <c r="R14" t="n">
-        <v>6991565</v>
+        <v>6991437</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1940,6 +1930,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Mer än 20 plantor</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1966,32 +1961,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132050865</v>
+        <v>132050873</v>
       </c>
       <c r="B15" t="n">
-        <v>78339</v>
+        <v>99195</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2001,10 +1996,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478416</v>
+        <v>478326</v>
       </c>
       <c r="R15" t="n">
-        <v>6991566</v>
+        <v>6991422</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2037,6 +2032,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Mer än 50 plantor</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2063,10 +2063,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132050870</v>
+        <v>132050878</v>
       </c>
       <c r="B16" t="n">
-        <v>99118</v>
+        <v>99195</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478419</v>
+        <v>478412</v>
       </c>
       <c r="R16" t="n">
-        <v>6991510</v>
+        <v>6991427</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2134,6 +2134,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Mer än 25 st plantor</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2160,10 +2165,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132050873</v>
+        <v>132050879</v>
       </c>
       <c r="B17" t="n">
-        <v>99118</v>
+        <v>99195</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2195,10 +2200,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478326</v>
+        <v>478374</v>
       </c>
       <c r="R17" t="n">
-        <v>6991422</v>
+        <v>6991445</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2235,7 +2240,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Mer än 50 plantor</t>
+          <t>Utspritt 30 + plantor</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2262,45 +2267,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132050861</v>
+        <v>132616025</v>
       </c>
       <c r="B18" t="n">
-        <v>57953</v>
+        <v>99195</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Svartsjöarna, Jmt</t>
+          <t>Måläng, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478453</v>
+        <v>478349</v>
       </c>
       <c r="R18" t="n">
-        <v>6991448</v>
+        <v>6991433</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2327,17 +2332,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran</t>
+          <t>1 planta</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2364,45 +2369,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132616025</v>
+        <v>132050863</v>
       </c>
       <c r="B19" t="n">
-        <v>99130</v>
+        <v>78382</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Måläng, Jmt</t>
+          <t>Svartsjöarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
         <v>478349</v>
       </c>
       <c r="R19" t="n">
-        <v>6991433</v>
+        <v>6991499</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2429,17 +2434,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>1 planta</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2466,10 +2466,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132616026</v>
+        <v>132050865</v>
       </c>
       <c r="B20" t="n">
-        <v>89300</v>
+        <v>78382</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2477,34 +2477,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>510</v>
+        <v>228579</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Måläng, Jmt</t>
+          <t>Svartsjöarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478401</v>
+        <v>478416</v>
       </c>
       <c r="R20" t="n">
-        <v>6991457</v>
+        <v>6991566</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2531,12 +2531,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 10058-2026 artfynd.xlsx
+++ b/artfynd/A 10058-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132616026</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050881</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050854</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050855</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050856</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050849</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050851</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050858</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1555,6 +1600,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050860</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1657,6 +1707,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050861</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1754,6 +1809,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050870</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1856,6 +1916,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050871</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1958,6 +2023,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050872</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2060,6 +2130,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050873</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2162,6 +2237,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050878</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2264,6 +2344,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050879</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2366,6 +2451,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132616025</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2463,6 +2553,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050863</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2560,8 +2655,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050865</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>